--- a/results/Int All Data 0.6/Rando_3_permute.xlsx
+++ b/results/Int All Data 0.6/Rando_3_permute.xlsx
@@ -440,13 +440,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6891891891891893</v>
+        <v>0.6652806652806653</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -456,1531 +456,1531 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6777546777546778</v>
+        <v>0.6642411642411643</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6798336798336798</v>
+        <v>0.6642411642411643</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6985446985446986</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.685031185031185</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6871101871101871</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6725571725571726</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6725571725571726</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6746361746361746</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6735966735966736</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6673596673596673</v>
+        <v>0.66008316008316</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6704781704781705</v>
+        <v>0.6632016632016632</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6694386694386695</v>
+        <v>0.658004158004158</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6694386694386695</v>
+        <v>0.6621621621621622</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6694386694386695</v>
+        <v>0.6632016632016632</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6694386694386695</v>
+        <v>0.6746361746361746</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6694386694386695</v>
+        <v>0.6746361746361746</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6704781704781705</v>
+        <v>0.6683991683991684</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6704781704781705</v>
+        <v>0.6597300527385273</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6704781704781705</v>
+        <v>0.6566115496200242</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6652806652806653</v>
+        <v>0.6566115496200242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6652806652806653</v>
+        <v>0.6566115496200242</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6725571725571726</v>
+        <v>0.6572979433148924</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6798336798336798</v>
+        <v>0.6614559474728967</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6746361746361746</v>
+        <v>0.6624954485123977</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.6624954485123977</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6735966735966736</v>
+        <v>0.6579843370097608</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6652806652806653</v>
+        <v>0.6569448359702597</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6621621621621622</v>
+        <v>0.6694188484442722</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6632016632016632</v>
+        <v>0.6721842442181425</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6642411642411643</v>
+        <v>0.6721842442181425</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6642411642411643</v>
+        <v>0.6721842442181425</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6652806652806653</v>
+        <v>0.6742632462971446</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6611226611226612</v>
+        <v>0.6742632462971446</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6611226611226612</v>
+        <v>0.6742632462971446</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.659043659043659</v>
+        <v>0.6742632462971446</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.659043659043659</v>
+        <v>0.6732237452576435</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.655925155925156</v>
+        <v>0.6683793474047711</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6528066528066528</v>
+        <v>0.6683793474047711</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6528066528066528</v>
+        <v>0.6704583494837733</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6528066528066528</v>
+        <v>0.6704583494837733</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6517671517671517</v>
+        <v>0.6704583494837733</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6507276507276507</v>
+        <v>0.6704583494837733</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6507276507276507</v>
+        <v>0.6725373515627753</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6507276507276507</v>
+        <v>0.6728904589074081</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6455301455301455</v>
+        <v>0.6728904589074081</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6455301455301455</v>
+        <v>0.6728904589074081</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6455301455301455</v>
+        <v>0.6728904589074081</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6496881496881497</v>
+        <v>0.6704583494837733</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6462165392250138</v>
+        <v>0.6704583494837733</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6430980361065106</v>
+        <v>0.6676929537099029</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6406659266828758</v>
+        <v>0.6666534526704019</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6406659266828758</v>
+        <v>0.670811456828406</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6475893266147503</v>
+        <v>0.6676929537099029</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6475893266147503</v>
+        <v>0.6676929537099029</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6472362192701175</v>
+        <v>0.6531399391568884</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6472362192701175</v>
+        <v>0.6507078297332535</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6399597119936102</v>
+        <v>0.6462165392250138</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6402929983438458</v>
+        <v>0.6503745433830179</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6406461056884786</v>
+        <v>0.6503745433830179</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6440978951572172</v>
+        <v>0.6455301455301455</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.500666572700471</v>
+        <v>0.6455301455301455</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.49925414332194</v>
+        <v>0.6486486486486487</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4999603580112055</v>
+        <v>0.6465696465696466</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4964094635704805</v>
+        <v>0.6486486486486487</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4918388890846518</v>
+        <v>0.6486486486486487</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4907795670507535</v>
+        <v>0.6507276507276507</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4921721754348873</v>
+        <v>0.6496881496881497</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4921721754348873</v>
+        <v>0.6496881496881497</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4932116764743883</v>
+        <v>0.6316635246719993</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4932116764743883</v>
+        <v>0.6503745433830179</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4932116764743883</v>
+        <v>0.592848878865828</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4878357823273077</v>
+        <v>0.592848878865828</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4849316395926566</v>
+        <v>0.5932019862104607</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4849316395926566</v>
+        <v>0.5921624851709597</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.484225424903391</v>
+        <v>0.6025574955659702</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4856180332875248</v>
+        <v>0.6025574955659702</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4919504739419994</v>
+        <v>0.601517994526469</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4915973665973666</v>
+        <v>0.6025574955659702</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4850667159989194</v>
+        <v>0.600478493486968</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4744177032312625</v>
+        <v>0.6060291060291061</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4671338548457192</v>
+        <v>0.5862785862785863</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4671338548457192</v>
+        <v>0.5966735966735967</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4736248634553719</v>
+        <v>0.5966735966735967</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4682687903026886</v>
+        <v>0.5966735966735967</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5163993034755747</v>
+        <v>0.5966735966735967</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5315792487402657</v>
+        <v>0.603950103950104</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.4994934634765144</v>
+        <v>0.603950103950104</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5055917227527398</v>
+        <v>0.603950103950104</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5828282650316549</v>
+        <v>0.605656177690076</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5762146599011005</v>
+        <v>0.6333695984119714</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5720764767374937</v>
+        <v>0.6150116870455853</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5720764767374937</v>
+        <v>0.6216216216216216</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5565001115848573</v>
+        <v>0.6216216216216216</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5608093425890036</v>
+        <v>0.5945945945945946</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.533957033957034</v>
+        <v>0.553014553014553</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5792428673784606</v>
+        <v>0.5239085239085239</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5792428673784606</v>
+        <v>0.5114345114345115</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5893207418631148</v>
+        <v>0.5114345114345115</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5893207418631148</v>
+        <v>0.5114345114345115</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5954388221337374</v>
+        <v>0.5135135135135135</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5954388221337374</v>
+        <v>0.5079629009713755</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6292270105829427</v>
+        <v>0.5048443978528724</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5705120864019169</v>
+        <v>0.526654098687997</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5155176362803482</v>
+        <v>0.526654098687997</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.515870743624981</v>
+        <v>0.5328911049250032</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4990331759399556</v>
+        <v>0.5072765072765073</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4648918801461174</v>
+        <v>0.5031185031185031</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4662250255470595</v>
+        <v>0.5024122884292376</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4662250255470595</v>
+        <v>0.5024122884292376</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4761281816366563</v>
+        <v>0.5103751894006131</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4979775244605753</v>
+        <v>0.5085700106886547</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.603538267733183</v>
+        <v>0.508216903344022</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.603538267733183</v>
+        <v>0.5064910086096527</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6082835606140691</v>
+        <v>0.5071972232989183</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6070583295159566</v>
+        <v>0.5331054653088552</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6129458989628481</v>
+        <v>0.533164928292047</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6122595052679798</v>
+        <v>0.533164928292047</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6144537627588476</v>
+        <v>0.533164928292047</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6157869081597895</v>
+        <v>0.5196712357729307</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6115136485899197</v>
+        <v>0.5304193535125739</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6077880357541374</v>
+        <v>0.5293402104842783</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6111803622396843</v>
+        <v>0.5358708610827255</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5896371436625674</v>
+        <v>0.5290465661228373</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6017022563632733</v>
+        <v>0.5318317828911049</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6199845543065882</v>
+        <v>0.5304391745069712</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.620337661651221</v>
+        <v>0.5248687409704359</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6184766905105888</v>
+        <v>0.5248687409704359</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5971874743061184</v>
+        <v>0.5213376675241082</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5971874743061184</v>
+        <v>0.5206512738292399</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5971874743061184</v>
+        <v>0.5206512738292399</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5975405816507511</v>
+        <v>0.5269081010606435</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6078401576282932</v>
+        <v>0.5258686000211424</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.6078401576282932</v>
+        <v>0.5258686000211424</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.6041541867813054</v>
+        <v>0.5303400695349848</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.6053324347815874</v>
+        <v>0.5951980337573558</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.6053324347815874</v>
+        <v>0.5681710067303287</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.6057846470982065</v>
+        <v>0.5980030715200206</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.6037056450192043</v>
+        <v>0.5681908277247261</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5868357764544205</v>
+        <v>0.5681908277247261</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5821462760022083</v>
+        <v>0.5657785392954884</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5820868130190164</v>
+        <v>0.5909805666161598</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5597925989875143</v>
+        <v>0.5813908758824013</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5597925989875143</v>
+        <v>0.536791436155843</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5525718841396807</v>
+        <v>0.5821528830003406</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5529249914843135</v>
+        <v>0.5792487402656894</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5203510224696666</v>
+        <v>0.5792487402656894</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5275284247741875</v>
+        <v>0.5838354651913974</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5275680667629821</v>
+        <v>0.5747537792029318</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5019982498796058</v>
+        <v>0.5747537792029318</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5110168023303616</v>
+        <v>0.5016355990932262</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5100529147139317</v>
+        <v>0.4938312660770288</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5007965103304086</v>
+        <v>0.4920855503482622</v>
       </c>
     </row>
   </sheetData>
